--- a/job-title-filters.xlsx
+++ b/job-title-filters.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -89,7 +91,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -115,6 +117,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3063,85 +3067,85 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="4" t="inlineStr">
         <is>
           <t>IT Support</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
         <is>
           <t>IT-department non-fit (helpdesk/support, not engineering)</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="4" t="inlineStr">
         <is>
           <t>Support Specialist</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
         <is>
           <t>IT-department non-fit (helpdesk/support, not engineering)</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="4" t="inlineStr">
         <is>
           <t>Help Desk</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
         <is>
           <t>IT-department non-fit (helpdesk/support, not engineering)</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="4" t="inlineStr">
         <is>
           <t>Desktop Support</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
         <is>
           <t>IT-department non-fit (helpdesk/support, not engineering)</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="4" t="inlineStr">
         <is>
           <t>Service Desk</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
         <is>
           <t>IT-department non-fit (helpdesk/support, not engineering)</t>
         </is>
@@ -3160,7 +3164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="4" min="1" max="1"/>
@@ -3197,6 +3201,846 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Community Engagement Lead</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Community Support Forecasting and Demand Planning Analyst</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Creative Lead, Photo</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Lead, Advanced Analytics, Product</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Operations Data &amp; Technology Strategy Lead</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Process &amp; Tools Scalability Specialist </t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Programs and Business Operations Lead</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Programs &amp; Business Operations Lead, Airbnb Services</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Regulatory Operations Lead</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Workforce Management, Manila</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Accounting Technical Solutions Lead</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Audit &amp; Regulatory Management Lead, Regulatory Affairs</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>AV Builds and Operations</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Brand partnerships &amp; strategy lead</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Capital &amp; Liquidity Risk Lead</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Compensation Business Partner, Core</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Corporate Accountant</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Crypto Product Accountant</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Data Analyst, Payments Performance</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Data Governance Lead</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Deal Pricing</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Enterprise Risk Management Lead</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Finance and Strategy Partner</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Finance &amp; Strategy Analyst</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Finance &amp; Strategy Partner</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Accountant, Insurance and Investments</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Analytics Lead, Market Insights</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Analytics Lead, Marketplace Strategy</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Analytics Lead, Safety &amp; Customer Care</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Applied Scientist- Pricing, Dynamic Pricing &amp; Offer Selection</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Data Analyst - Global Growth Luxury Strategy</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Data Analyst, Operations Planning</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Head of Claims</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Operations Associate</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Operations Associate, Flexdrive</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Operations Lead</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Senior Accountant, Fleet Accounting</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Senior Billing Specialist</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Senior Illustrator, Design Foundations &amp; AI Transformation</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
